--- a/ARM Functions/Item Edits/Ability Capsule.xlsx
+++ b/ARM Functions/Item Edits/Ability Capsule.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Item Edits\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCB32A7-5301-4AD4-8B04-8379D3DC4C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE228EF4-8D4C-44EA-8204-241CA172C4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16457" windowHeight="17914" activeTab="1" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="-16457" yWindow="0" windowWidth="16457" windowHeight="17914" activeTab="1" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="edited bag.cro" sheetId="14" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="original bag.cro" sheetId="6" r:id="rId3"/>
     <sheet name="original code.bin" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="302">
   <si>
     <t>Address</t>
   </si>
@@ -254,9 +254,6 @@
     <t>Current slot (out of 0/1/2), here it is 0</t>
   </si>
   <si>
-    <t>same for both</t>
-  </si>
-  <si>
     <t>0C0090E5</t>
   </si>
   <si>
@@ -939,6 +936,15 @@
   </si>
   <si>
     <t>US in-file</t>
+  </si>
+  <si>
+    <t>Set low bit that toggles 0/1</t>
+  </si>
+  <si>
+    <t>set higher bit that toggles hidden to 0</t>
+  </si>
+  <si>
+    <t>This is the higher bit that toggles Hidden</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1076,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1147,7 +1153,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1513,10 +1518,10 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="C2" s="2" t="str">
         <f>_xlfn.CONCAT("b 0x",A39)</f>
@@ -1531,16 +1536,16 @@
     </row>
     <row r="4" spans="1:6" ht="31.75">
       <c r="A4" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>150</v>
-      </c>
       <c r="D4" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1549,10 +1554,10 @@
         <v>00009A40</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D5" s="27"/>
     </row>
@@ -1575,14 +1580,14 @@
         <v>00009A48</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C7" s="8" t="str">
         <f>_xlfn.CONCAT("beq 0x",A44)</f>
         <v>beq 0x00009ADC</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1591,7 +1596,7 @@
         <v>00009A4C</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C8" s="8" t="str">
         <f>_xlfn.CONCAT("b 0x",A25)</f>
@@ -1605,10 +1610,10 @@
         <v>00009A50</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -1619,10 +1624,10 @@
         <v>00009A54</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -1633,10 +1638,10 @@
         <v>00009A58</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -1647,7 +1652,7 @@
         <v>00009A5C</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>35</v>
@@ -1674,7 +1679,7 @@
         <v>00009A64</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C14" s="5" t="str">
         <f>_xlfn.CONCAT("beq 0x",A58)</f>
@@ -1689,10 +1694,10 @@
         <v>00009A68</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1701,10 +1706,10 @@
         <v>00009A6C</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1713,10 +1718,10 @@
         <v>00009A70</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1725,10 +1730,10 @@
         <v>00009A74</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1737,10 +1742,10 @@
         <v>00009A78</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1749,10 +1754,10 @@
         <v>00009A7C</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D20" s="29"/>
     </row>
@@ -1762,10 +1767,10 @@
         <v>00009A80</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D21" s="29"/>
       <c r="E21" s="4"/>
@@ -1776,10 +1781,10 @@
         <v>00009A84</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D22" s="29"/>
       <c r="E22" s="4"/>
@@ -1791,10 +1796,10 @@
         <v>00009A88</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D23" s="29"/>
       <c r="E23" s="4"/>
@@ -1806,10 +1811,10 @@
         <v>00009A8C</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D24" s="29"/>
       <c r="E24" s="4"/>
@@ -1821,10 +1826,10 @@
         <v>00009A90</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D25" s="30"/>
     </row>
@@ -1834,13 +1839,13 @@
         <v>00009A94</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1855,7 +1860,7 @@
         <v>10</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F27" s="4"/>
     </row>
@@ -1865,13 +1870,13 @@
         <v>00009A9C</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1880,13 +1885,13 @@
         <v>00009AA0</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C29" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="D29" s="30" t="s">
         <v>253</v>
-      </c>
-      <c r="D29" s="30" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1895,13 +1900,13 @@
         <v>00009AA4</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -1910,10 +1915,10 @@
         <v>00009AA8</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D31" s="30"/>
     </row>
@@ -1923,10 +1928,10 @@
         <v>00009AAC</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D32" s="30"/>
     </row>
@@ -1936,13 +1941,13 @@
         <v>00009AB0</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D33" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1951,10 +1956,10 @@
         <v>00009AB4</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D34" s="35"/>
     </row>
@@ -1964,10 +1969,10 @@
         <v>00009AB8</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D35" s="35"/>
     </row>
@@ -1977,10 +1982,10 @@
         <v>00009ABC</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" s="35"/>
     </row>
@@ -1990,10 +1995,10 @@
         <v>00009AC0</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D37" s="35"/>
     </row>
@@ -2003,10 +2008,10 @@
         <v>00009AC4</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D38" s="35"/>
     </row>
@@ -2016,10 +2021,10 @@
         <v>00009AC8</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D39" s="35"/>
     </row>
@@ -2029,10 +2034,10 @@
         <v>00009ACC</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D40" s="35"/>
     </row>
@@ -2042,10 +2047,10 @@
         <v>00009AD0</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D41" s="35"/>
     </row>
@@ -2055,7 +2060,7 @@
         <v>00009AD4</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2064,7 +2069,7 @@
         <v>00009AD8</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2073,13 +2078,13 @@
         <v>00009ADC</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2088,10 +2093,10 @@
         <v>00009AE0</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D45" s="36"/>
     </row>
@@ -2101,10 +2106,10 @@
         <v>00009AE4</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D46" s="36"/>
     </row>
@@ -2114,7 +2119,7 @@
         <v>00009AE8</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>37</v>
@@ -2127,10 +2132,10 @@
         <v>00009AEC</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D48" s="36"/>
     </row>
@@ -2140,10 +2145,10 @@
         <v>00009AF0</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D49" s="36"/>
     </row>
@@ -2153,10 +2158,10 @@
         <v>00009AF4</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D50" s="36"/>
     </row>
@@ -2166,10 +2171,10 @@
         <v>00009AF8</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D51" s="36"/>
     </row>
@@ -2179,10 +2184,10 @@
         <v>00009AFC</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D52" s="36"/>
     </row>
@@ -2192,7 +2197,7 @@
         <v>00009B00</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C53" s="12"/>
       <c r="D53" s="31"/>
@@ -2203,7 +2208,7 @@
         <v>00009B04</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C54" s="12"/>
       <c r="D54" s="31"/>
@@ -2214,7 +2219,7 @@
         <v>00009B08</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C55" s="12"/>
       <c r="D55" s="31"/>
@@ -2225,7 +2230,7 @@
         <v>00009B0C</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C56" s="12"/>
       <c r="D56" s="31"/>
@@ -2237,7 +2242,7 @@
         <v>00009B10</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C57" s="12"/>
       <c r="D57" s="31"/>
@@ -2251,16 +2256,16 @@
     </row>
     <row r="60" spans="1:11" ht="31.75">
       <c r="A60" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B60" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F60" s="5"/>
     </row>
@@ -2270,10 +2275,10 @@
         <v>0000DCEC</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D61" s="27"/>
       <c r="F61" s="5"/>
@@ -2298,14 +2303,14 @@
         <v>0000DCF4</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C63" s="8" t="str">
         <f>_xlfn.CONCAT("beq 0x",A77)</f>
         <v>beq 0x0000DD2C</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F63" s="5"/>
     </row>
@@ -2315,13 +2320,13 @@
         <v>0000DCF8</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C64" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D64" s="27" t="s">
         <v>247</v>
-      </c>
-      <c r="D64" s="27" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2330,13 +2335,13 @@
         <v>0000DCFC</v>
       </c>
       <c r="B65" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C65" s="42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D65" s="43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2358,10 +2363,10 @@
         <v>0000DD04</v>
       </c>
       <c r="B67" s="41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C67" s="42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D67" s="43"/>
     </row>
@@ -2371,7 +2376,7 @@
         <v>0000DD08</v>
       </c>
       <c r="B68" s="41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C68" s="42" t="s">
         <v>35</v>
@@ -2400,7 +2405,7 @@
         <v>19</v>
       </c>
       <c r="C70" s="42" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D70" s="43"/>
     </row>
@@ -2410,10 +2415,10 @@
         <v>0000DD14</v>
       </c>
       <c r="B71" s="40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C71" s="40" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D71" s="43"/>
     </row>
@@ -2423,7 +2428,7 @@
         <v>0000DD18</v>
       </c>
       <c r="B72" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C72" s="37"/>
       <c r="D72" s="38"/>
@@ -2434,7 +2439,7 @@
         <v>0000DD1C</v>
       </c>
       <c r="B73" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C73" s="37"/>
       <c r="D73" s="38"/>
@@ -2445,7 +2450,7 @@
         <v>0000DD20</v>
       </c>
       <c r="B74" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="38"/>
@@ -2456,7 +2461,7 @@
         <v>0000DD24</v>
       </c>
       <c r="B75" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C75" s="37"/>
       <c r="D75" s="38"/>
@@ -2467,7 +2472,7 @@
         <v>0000DD28</v>
       </c>
       <c r="B76" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C76" s="37"/>
       <c r="D76" s="38"/>
@@ -2481,10 +2486,10 @@
         <v>14</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D77" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2505,15 +2510,15 @@
     <col min="2" max="2" width="12.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="33.92578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="46.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="48.92578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="12.140625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.92578125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="48" customFormat="1">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>20</v>
@@ -2528,7 +2533,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>23</v>
@@ -2562,10 +2567,10 @@
         <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F3" s="3" t="str">
         <f>DEC2HEX(HEX2DEC(G3)-HEX2DEC(100000),8)</f>
@@ -2575,7 +2580,7 @@
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I3" s="2" t="str">
         <f>D3</f>
@@ -2623,7 +2628,7 @@
         <v>00321678</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>30</v>
@@ -2638,7 +2643,7 @@
         <v>00321678</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>30</v>
@@ -2654,13 +2659,13 @@
         <v>0032167C</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>31</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F6" s="6" t="str">
         <f t="shared" si="2"/>
@@ -2671,10 +2676,10 @@
         <v>0032167C</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2718,13 +2723,13 @@
         <v>00321684</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F8" s="6" t="str">
         <f t="shared" si="2"/>
@@ -2735,10 +2740,10 @@
         <v>00321684</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2751,13 +2756,13 @@
         <v>00321688</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F9" s="6" t="str">
         <f t="shared" si="2"/>
@@ -2768,10 +2773,10 @@
         <v>00321688</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2784,14 +2789,14 @@
         <v>0032168C</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D10" s="6" t="str">
         <f>_xlfn.CONCAT("beq 0x",B18)</f>
         <v>beq 0x003216AC</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F10" s="6" t="str">
         <f t="shared" si="2"/>
@@ -2802,7 +2807,7 @@
         <v>0032168C</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I10" s="6" t="str">
         <f>_xlfn.CONCAT("beq 0x",G18)</f>
@@ -2819,7 +2824,7 @@
         <v>00321690</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>33</v>
@@ -2834,7 +2839,7 @@
         <v>00321690</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>33</v>
@@ -2850,13 +2855,13 @@
         <v>00321694</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>34</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F12" s="8" t="str">
         <f t="shared" si="2"/>
@@ -2867,10 +2872,10 @@
         <v>00321694</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -2889,7 +2894,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F13" s="8" t="str">
         <f t="shared" si="2"/>
@@ -2916,13 +2921,13 @@
         <v>0032169C</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F14" s="8" t="str">
         <f t="shared" si="2"/>
@@ -2933,10 +2938,10 @@
         <v>0032169C</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -2949,13 +2954,13 @@
         <v>003216A0</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F15" s="8" t="str">
         <f t="shared" si="2"/>
@@ -2966,10 +2971,10 @@
         <v>003216A0</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2982,13 +2987,13 @@
         <v>003216A4</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F16" s="8" t="str">
         <f t="shared" si="2"/>
@@ -2999,10 +3004,10 @@
         <v>003216A4</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -3015,13 +3020,13 @@
         <v>003216A8</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F17" s="8" t="str">
         <f t="shared" si="2"/>
@@ -3032,10 +3037,10 @@
         <v>003216A8</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -3048,7 +3053,7 @@
         <v>003216AC</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>33</v>
@@ -3063,7 +3068,7 @@
         <v>003216AC</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>33</v>
@@ -3079,13 +3084,13 @@
         <v>003216B0</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F19" s="12" t="str">
         <f t="shared" si="2"/>
@@ -3096,10 +3101,10 @@
         <v>003216B0</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I19" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -3112,7 +3117,7 @@
         <v>003216B4</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>43</v>
@@ -3127,10 +3132,10 @@
         <v>003216B4</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I20" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -3143,7 +3148,7 @@
         <v>003216B8</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D21" s="16" t="s">
         <v>44</v>
@@ -3158,7 +3163,7 @@
         <v>003216B8</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>44</v>
@@ -3174,7 +3179,7 @@
         <v>003216BC</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>33</v>
@@ -3189,7 +3194,7 @@
         <v>003216BC</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I22" s="16" t="s">
         <v>33</v>
@@ -3205,7 +3210,7 @@
         <v>003216C0</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>45</v>
@@ -3220,10 +3225,10 @@
         <v>003216C0</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3236,7 +3241,7 @@
         <v>003216C4</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>46</v>
@@ -3251,7 +3256,7 @@
         <v>003216C4</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I24" s="17" t="s">
         <v>46</v>
@@ -3267,10 +3272,10 @@
         <v>003216C8</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E25" s="17"/>
       <c r="F25" s="17" t="str">
@@ -3282,7 +3287,7 @@
         <v>003216C8</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I25" s="17" t="s">
         <v>47</v>
@@ -3298,7 +3303,7 @@
         <v>003216CC</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>48</v>
@@ -3313,7 +3318,7 @@
         <v>003216CC</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I26" s="17" t="s">
         <v>48</v>
@@ -3329,7 +3334,7 @@
         <v>003216D0</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D27" s="17" t="s">
         <v>49</v>
@@ -3344,7 +3349,7 @@
         <v>003216D0</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I27" s="17" t="s">
         <v>49</v>
@@ -3360,7 +3365,7 @@
         <v>003216D4</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D28" s="18" t="s">
         <v>32</v>
@@ -3375,7 +3380,7 @@
         <v>003216D4</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>32</v>
@@ -3391,7 +3396,7 @@
         <v>003216D8</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D29" s="18" t="s">
         <v>33</v>
@@ -3406,7 +3411,7 @@
         <v>003216D8</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I29" s="18" t="s">
         <v>33</v>
@@ -3422,13 +3427,13 @@
         <v>003216DC</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F30" s="18" t="str">
         <f t="shared" si="2"/>
@@ -3439,10 +3444,10 @@
         <v>003216DC</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3455,7 +3460,7 @@
         <v>003216E0</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D31" s="18" t="s">
         <v>51</v>
@@ -3470,7 +3475,7 @@
         <v>003216E0</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I31" s="18" t="s">
         <v>51</v>
@@ -3486,13 +3491,13 @@
         <v>003216E4</v>
       </c>
       <c r="C32" s="45" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F32" s="44" t="str">
         <f t="shared" si="2"/>
@@ -3503,10 +3508,10 @@
         <v>003216E4</v>
       </c>
       <c r="H32" s="45" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I32" s="44" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -3519,13 +3524,13 @@
         <v>003216E8</v>
       </c>
       <c r="C33" s="44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F33" s="44" t="str">
         <f t="shared" si="2"/>
@@ -3536,10 +3541,10 @@
         <v>003216E8</v>
       </c>
       <c r="H33" s="44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I33" s="44" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -3552,13 +3557,13 @@
         <v>003216EC</v>
       </c>
       <c r="C34" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F34" s="44" t="str">
         <f t="shared" si="2"/>
@@ -3569,10 +3574,10 @@
         <v>003216EC</v>
       </c>
       <c r="H34" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I34" s="44" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -3585,7 +3590,7 @@
         <v>003216F0</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D35" s="44" t="s">
         <v>33</v>
@@ -3600,7 +3605,7 @@
         <v>003216F0</v>
       </c>
       <c r="H35" s="44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I35" s="44" t="s">
         <v>33</v>
@@ -3616,13 +3621,13 @@
         <v>003216F4</v>
       </c>
       <c r="C36" s="44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D36" s="44" t="s">
         <v>55</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F36" s="44" t="str">
         <f t="shared" si="2"/>
@@ -3633,7 +3638,7 @@
         <v>003216F4</v>
       </c>
       <c r="H36" s="44" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I36" s="44" t="s">
         <v>55</v>
@@ -3649,12 +3654,14 @@
         <v>003216F8</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D37" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E37" s="13"/>
+      <c r="E37" s="13" t="s">
+        <v>301</v>
+      </c>
       <c r="F37" s="13" t="str">
         <f t="shared" si="2"/>
         <v>002216F8</v>
@@ -3664,7 +3671,7 @@
         <v>003216F8</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I37" s="13" t="s">
         <v>33</v>
@@ -3680,13 +3687,13 @@
         <v>003216FC</v>
       </c>
       <c r="C38" s="46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F38" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3697,10 +3704,10 @@
         <v>003216FC</v>
       </c>
       <c r="H38" s="46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -3713,13 +3720,13 @@
         <v>00321700</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F39" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3730,10 +3737,10 @@
         <v>00321700</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -3746,13 +3753,13 @@
         <v>00321704</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D40" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F40" s="13" t="str">
         <f t="shared" si="2"/>
@@ -3763,10 +3770,10 @@
         <v>00321704</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -3779,7 +3786,7 @@
         <v>00321708</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>56</v>
@@ -3794,7 +3801,7 @@
         <v>00321708</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I41" s="13" t="s">
         <v>56</v>
@@ -3810,7 +3817,7 @@
         <v>0032170C</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>33</v>
@@ -3824,7 +3831,7 @@
         <v>0032170C</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>33</v>
@@ -3840,7 +3847,7 @@
         <v>00321710</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>57</v>
@@ -3854,7 +3861,7 @@
         <v>00321710</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>57</v>
@@ -3870,7 +3877,7 @@
         <v>00321714</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D44" s="2" t="str">
         <f>SUBSTITUTE(D3,"push","pop")</f>
@@ -3885,7 +3892,7 @@
         <v>00321714</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I44" s="2" t="str">
         <f>SUBSTITUTE(I3,"push","pop")</f>
@@ -3902,13 +3909,13 @@
         <v>00321718</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="F45" s="2" t="str">
         <f t="shared" si="2"/>
@@ -3919,10 +3926,10 @@
         <v>00321718</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -3970,16 +3977,16 @@
     </row>
     <row r="2" spans="1:6" ht="31.75">
       <c r="A2" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>150</v>
-      </c>
       <c r="D2" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4014,14 +4021,14 @@
         <v>00009A48</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C5" s="8" t="str">
         <f>_xlfn.CONCAT("bne 0x",A42)</f>
         <v>bne 0x00009ADC</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4030,7 +4037,7 @@
         <v>00009A4C</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C6" s="8" t="str">
         <f>_xlfn.CONCAT("b 0x",A23)</f>
@@ -4044,10 +4051,10 @@
         <v>00009A50</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -4058,10 +4065,10 @@
         <v>00009A54</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -4072,10 +4079,10 @@
         <v>00009A58</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -4086,7 +4093,7 @@
         <v>00009A5C</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>35</v>
@@ -4113,7 +4120,7 @@
         <v>00009A64</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C12" s="5" t="str">
         <f>_xlfn.CONCAT("beq 0x",A56)</f>
@@ -4128,10 +4135,10 @@
         <v>00009A68</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -4140,10 +4147,10 @@
         <v>00009A6C</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -4152,10 +4159,10 @@
         <v>00009A70</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -4164,10 +4171,10 @@
         <v>00009A74</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4176,10 +4183,10 @@
         <v>00009A78</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4188,10 +4195,10 @@
         <v>00009A7C</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D18" s="29"/>
     </row>
@@ -4201,10 +4208,10 @@
         <v>00009A80</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D19" s="29"/>
       <c r="E19" s="4"/>
@@ -4215,10 +4222,10 @@
         <v>00009A84</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D20" s="29"/>
       <c r="E20" s="4"/>
@@ -4230,10 +4237,10 @@
         <v>00009A88</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D21" s="29"/>
       <c r="E21" s="4"/>
@@ -4245,10 +4252,10 @@
         <v>00009A8C</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D22" s="29"/>
       <c r="E22" s="4"/>
@@ -4260,10 +4267,10 @@
         <v>00009A90</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D23" s="29"/>
     </row>
@@ -4273,13 +4280,13 @@
         <v>00009A94</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D24" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -4294,7 +4301,7 @@
         <v>16</v>
       </c>
       <c r="D25" s="30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F25" s="4"/>
     </row>
@@ -4317,13 +4324,13 @@
         <v>00009AA0</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -4332,13 +4339,13 @@
         <v>00009AA4</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>35</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -4347,13 +4354,13 @@
         <v>00009AA8</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -4362,13 +4369,13 @@
         <v>00009AAC</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -4377,10 +4384,10 @@
         <v>00009AB0</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D31" s="34"/>
     </row>
@@ -4390,10 +4397,10 @@
         <v>00009AB4</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D32" s="34"/>
     </row>
@@ -4403,13 +4410,13 @@
         <v>00009AB8</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C33" s="24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D33" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -4418,10 +4425,10 @@
         <v>00009ABC</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D34" s="35"/>
     </row>
@@ -4431,10 +4438,10 @@
         <v>00009AC0</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C35" s="24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D35" s="35"/>
     </row>
@@ -4444,10 +4451,10 @@
         <v>00009AC4</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D36" s="35"/>
     </row>
@@ -4457,10 +4464,10 @@
         <v>00009AC8</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C37" s="24" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D37" s="35"/>
     </row>
@@ -4470,10 +4477,10 @@
         <v>00009ACC</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D38" s="35"/>
     </row>
@@ -4483,10 +4490,10 @@
         <v>00009AD0</v>
       </c>
       <c r="B39" s="25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C39" s="24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D39" s="35"/>
     </row>
@@ -4496,10 +4503,10 @@
         <v>00009AD4</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D40" s="35"/>
     </row>
@@ -4509,10 +4516,10 @@
         <v>00009AD8</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C41" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D41" s="35"/>
     </row>
@@ -4522,13 +4529,13 @@
         <v>00009ADC</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>36</v>
       </c>
       <c r="D42" s="36" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -4537,10 +4544,10 @@
         <v>00009AE0</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D43" s="36"/>
     </row>
@@ -4550,10 +4557,10 @@
         <v>00009AE4</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D44" s="36"/>
     </row>
@@ -4563,7 +4570,7 @@
         <v>00009AE8</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C45" s="10" t="s">
         <v>37</v>
@@ -4576,10 +4583,10 @@
         <v>00009AEC</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D46" s="36"/>
     </row>
@@ -4589,10 +4596,10 @@
         <v>00009AF0</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D47" s="36"/>
     </row>
@@ -4602,10 +4609,10 @@
         <v>00009AF4</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D48" s="36"/>
     </row>
@@ -4615,10 +4622,10 @@
         <v>00009AF8</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D49" s="36"/>
     </row>
@@ -4628,10 +4635,10 @@
         <v>00009AFC</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D50" s="36"/>
     </row>
@@ -4647,7 +4654,7 @@
         <v>15</v>
       </c>
       <c r="D51" s="31" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -4656,10 +4663,10 @@
         <v>00009B04</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D52" s="31"/>
     </row>
@@ -4669,13 +4676,13 @@
         <v>00009B08</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D53" s="31" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -4698,13 +4705,13 @@
         <v>00009B10</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K55" s="4"/>
     </row>
@@ -4716,16 +4723,16 @@
     </row>
     <row r="58" spans="1:11" ht="31.75">
       <c r="A58" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B58" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F58" s="5"/>
     </row>
@@ -4763,14 +4770,14 @@
         <v>0000DCF4</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C61" s="8" t="str">
         <f>_xlfn.CONCAT("bne 0x",A75)</f>
         <v>bne 0x0000DD2C</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F61" s="5"/>
     </row>
@@ -4780,7 +4787,7 @@
         <v>0000DCF8</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C62" s="8" t="str">
         <f>_xlfn.CONCAT("b 0x",A70)</f>
@@ -4794,13 +4801,13 @@
         <v>0000DCFC</v>
       </c>
       <c r="B63" s="41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C63" s="42" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D63" s="43" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -4822,10 +4829,10 @@
         <v>0000DD04</v>
       </c>
       <c r="B65" s="41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C65" s="42" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D65" s="43"/>
     </row>
@@ -4835,7 +4842,7 @@
         <v>0000DD08</v>
       </c>
       <c r="B66" s="41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C66" s="42" t="s">
         <v>35</v>
@@ -4864,7 +4871,7 @@
         <v>19</v>
       </c>
       <c r="C68" s="42" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D68" s="43"/>
     </row>
@@ -4874,10 +4881,10 @@
         <v>0000DD14</v>
       </c>
       <c r="B69" s="40" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C69" s="40" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D69" s="43"/>
     </row>
@@ -4887,7 +4894,7 @@
         <v>0000DD18</v>
       </c>
       <c r="B70" s="40" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C70" s="40" t="s">
         <v>48</v>
@@ -4900,13 +4907,13 @@
         <v>0000DD1C</v>
       </c>
       <c r="B71" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="C71" s="37" t="s">
+        <v>162</v>
+      </c>
+      <c r="D71" s="38" t="s">
         <v>238</v>
-      </c>
-      <c r="C71" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="D71" s="38" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -4921,7 +4928,7 @@
         <v>16</v>
       </c>
       <c r="D72" s="38" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -4946,10 +4953,10 @@
         <v>11</v>
       </c>
       <c r="C74" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D74" s="38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -4961,10 +4968,10 @@
         <v>14</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -5073,7 +5080,7 @@
         <v>00321678</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>30</v>
@@ -5084,7 +5091,7 @@
         <v>00321678</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>30</v>
@@ -5096,23 +5103,23 @@
         <v>0032167C</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E6" s="6" t="str">
         <f t="shared" si="1"/>
         <v>0032167C</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5121,7 +5128,7 @@
         <v>00321680</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>32</v>
@@ -5134,7 +5141,7 @@
         <v>00321680</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>32</v>
@@ -5146,7 +5153,7 @@
         <v>00321684</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>33</v>
@@ -5157,7 +5164,7 @@
         <v>00321684</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>33</v>
@@ -5169,7 +5176,7 @@
         <v>00321688</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>34</v>
@@ -5182,10 +5189,10 @@
         <v>00321688</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5194,7 +5201,7 @@
         <v>0032168C</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>35</v>
@@ -5205,7 +5212,7 @@
         <v>0032168C</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>35</v>
@@ -5217,21 +5224,21 @@
         <v>00321690</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="8" t="str">
         <f>_xlfn.CONCAT("beq 0x",A18)</f>
         <v>beq 0x003216AC</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E11" s="8" t="str">
         <f t="shared" si="1"/>
         <v>00321690</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G11" s="8" t="str">
         <f>_xlfn.CONCAT("beq 0x",E18)</f>
@@ -5244,7 +5251,7 @@
         <v>00321694</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>36</v>
@@ -5257,7 +5264,7 @@
         <v>00321694</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>36</v>
@@ -5292,7 +5299,7 @@
         <v>0032169C</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>37</v>
@@ -5303,7 +5310,7 @@
         <v>0032169C</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>37</v>
@@ -5315,7 +5322,7 @@
         <v>003216A0</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>38</v>
@@ -5326,7 +5333,7 @@
         <v>003216A0</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>38</v>
@@ -5338,7 +5345,7 @@
         <v>003216A4</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>39</v>
@@ -5349,7 +5356,7 @@
         <v>003216A4</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>39</v>
@@ -5361,7 +5368,7 @@
         <v>003216A8</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>40</v>
@@ -5372,7 +5379,7 @@
         <v>003216A8</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>40</v>
@@ -5384,20 +5391,20 @@
         <v>003216AC</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>41</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E18" s="11" t="str">
         <f t="shared" si="1"/>
         <v>003216AC</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>41</v>
@@ -5409,7 +5416,7 @@
         <v>003216B0</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" s="11" t="str">
         <f>_xlfn.CONCAT("beq 0x",A37)</f>
@@ -5423,7 +5430,7 @@
         <v>003216B0</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G19" s="11" t="str">
         <f>_xlfn.CONCAT("beq 0x",E37)</f>
@@ -5436,7 +5443,7 @@
         <v>003216B4</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>33</v>
@@ -5449,7 +5456,7 @@
         <v>003216B4</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G20" s="11" t="s">
         <v>33</v>
@@ -5461,7 +5468,7 @@
         <v>003216B8</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>42</v>
@@ -5474,7 +5481,7 @@
         <v>003216B8</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" s="11" t="s">
         <v>42</v>
@@ -5486,7 +5493,7 @@
         <v>003216BC</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>43</v>
@@ -5497,10 +5504,10 @@
         <v>003216BC</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5509,7 +5516,7 @@
         <v>003216C0</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="11" t="s">
         <v>44</v>
@@ -5520,7 +5527,7 @@
         <v>003216C0</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G23" s="11" t="s">
         <v>44</v>
@@ -5532,7 +5539,7 @@
         <v>003216C4</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C24" s="11" t="s">
         <v>33</v>
@@ -5543,7 +5550,7 @@
         <v>003216C4</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G24" s="11" t="s">
         <v>33</v>
@@ -5555,7 +5562,7 @@
         <v>003216C8</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>45</v>
@@ -5566,10 +5573,10 @@
         <v>003216C8</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -5578,7 +5585,7 @@
         <v>003216CC</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>46</v>
@@ -5589,7 +5596,7 @@
         <v>003216CC</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>46</v>
@@ -5601,7 +5608,7 @@
         <v>003216D0</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>47</v>
@@ -5612,7 +5619,7 @@
         <v>003216D0</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>47</v>
@@ -5624,7 +5631,7 @@
         <v>003216D4</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>48</v>
@@ -5635,7 +5642,7 @@
         <v>003216D4</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>48</v>
@@ -5647,20 +5654,20 @@
         <v>003216D8</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>49</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E29" s="11" t="str">
         <f t="shared" si="1"/>
         <v>003216D8</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>49</v>
@@ -5672,20 +5679,20 @@
         <v>003216DC</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>32</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E30" s="11" t="str">
         <f t="shared" si="1"/>
         <v>003216DC</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G30" s="11" t="s">
         <v>32</v>
@@ -5697,20 +5704,20 @@
         <v>003216E0</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" s="11" t="s">
         <v>33</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E31" s="11" t="str">
         <f t="shared" si="1"/>
         <v>003216E0</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>33</v>
@@ -5722,7 +5729,7 @@
         <v>003216E4</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>50</v>
@@ -5735,7 +5742,7 @@
         <v>003216E4</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G32" s="11" t="s">
         <v>50</v>
@@ -5747,7 +5754,7 @@
         <v>003216E8</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C33" s="11" t="s">
         <v>51</v>
@@ -5758,7 +5765,7 @@
         <v>003216E8</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>51</v>
@@ -5770,7 +5777,7 @@
         <v>003216EC</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>52</v>
@@ -5783,7 +5790,7 @@
         <v>003216EC</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>52</v>
@@ -5818,7 +5825,7 @@
         <v>003216F4</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36" s="11" t="str">
         <f>_xlfn.CONCAT("b 0x",A52)</f>
@@ -5832,7 +5839,7 @@
         <v>003216F4</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G36" s="11" t="str">
         <f>_xlfn.CONCAT("b 0x",E52)</f>
@@ -5845,7 +5852,7 @@
         <v>003216F8</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>33</v>
@@ -5858,7 +5865,7 @@
         <v>003216F8</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G37" s="12" t="s">
         <v>33</v>
@@ -5870,7 +5877,7 @@
         <v>003216FC</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>54</v>
@@ -5883,7 +5890,7 @@
         <v>003216FC</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G38" s="12" t="s">
         <v>54</v>
@@ -5895,7 +5902,7 @@
         <v>00321700</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>43</v>
@@ -5906,10 +5913,10 @@
         <v>00321700</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -5918,7 +5925,7 @@
         <v>00321704</v>
       </c>
       <c r="B40" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>44</v>
@@ -5929,7 +5936,7 @@
         <v>00321704</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>44</v>
@@ -5941,7 +5948,7 @@
         <v>00321708</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>33</v>
@@ -5952,7 +5959,7 @@
         <v>00321708</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G41" s="12" t="s">
         <v>33</v>
@@ -5964,7 +5971,7 @@
         <v>0032170C</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>45</v>
@@ -5975,10 +5982,10 @@
         <v>0032170C</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -5987,7 +5994,7 @@
         <v>00321710</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>46</v>
@@ -5998,7 +6005,7 @@
         <v>00321710</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G43" s="12" t="s">
         <v>46</v>
@@ -6010,7 +6017,7 @@
         <v>00321714</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>47</v>
@@ -6021,7 +6028,7 @@
         <v>00321714</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>47</v>
@@ -6033,7 +6040,7 @@
         <v>00321718</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>48</v>
@@ -6044,7 +6051,7 @@
         <v>00321718</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G45" s="12" t="s">
         <v>48</v>
@@ -6056,7 +6063,7 @@
         <v>0032171C</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>49</v>
@@ -6067,7 +6074,7 @@
         <v>0032171C</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G46" s="12" t="s">
         <v>49</v>
@@ -6079,7 +6086,7 @@
         <v>00321720</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>32</v>
@@ -6090,7 +6097,7 @@
         <v>00321720</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G47" s="12" t="s">
         <v>32</v>
@@ -6102,7 +6109,7 @@
         <v>00321724</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>33</v>
@@ -6113,7 +6120,7 @@
         <v>00321724</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G48" s="12" t="s">
         <v>33</v>
@@ -6125,7 +6132,7 @@
         <v>00321728</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>52</v>
@@ -6138,7 +6145,7 @@
         <v>00321728</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G49" s="12" t="s">
         <v>52</v>
@@ -6150,7 +6157,7 @@
         <v>0032172C</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>51</v>
@@ -6161,7 +6168,7 @@
         <v>0032172C</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G50" s="12" t="s">
         <v>51</v>
@@ -6173,7 +6180,7 @@
         <v>00321730</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>50</v>
@@ -6186,7 +6193,7 @@
         <v>00321730</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G51" s="12" t="s">
         <v>50</v>
@@ -6198,20 +6205,20 @@
         <v>00321734</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C52" s="13" t="s">
         <v>33</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>71</v>
+        <v>299</v>
       </c>
       <c r="E52" s="13" t="str">
         <f t="shared" si="1"/>
         <v>00321734</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G52" s="13" t="s">
         <v>33</v>
@@ -6223,7 +6230,7 @@
         <v>00321738</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C53" s="13" t="s">
         <v>55</v>
@@ -6234,7 +6241,7 @@
         <v>00321738</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>55</v>
@@ -6246,7 +6253,7 @@
         <v>0032173C</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C54" s="13" t="s">
         <v>33</v>
@@ -6257,7 +6264,7 @@
         <v>0032173C</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G54" s="13" t="s">
         <v>33</v>
@@ -6269,18 +6276,20 @@
         <v>00321740</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C55" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="13"/>
+      <c r="D55" s="13" t="s">
+        <v>300</v>
+      </c>
       <c r="E55" s="13" t="str">
         <f t="shared" si="1"/>
         <v>00321740</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>52</v>
@@ -6292,7 +6301,7 @@
         <v>00321744</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C56" s="13" t="s">
         <v>56</v>
@@ -6303,7 +6312,7 @@
         <v>00321744</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>56</v>
@@ -6315,7 +6324,7 @@
         <v>00321748</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C57" s="13" t="s">
         <v>33</v>
@@ -6326,7 +6335,7 @@
         <v>00321748</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>33</v>
@@ -6338,7 +6347,7 @@
         <v>0032174C</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C58" s="13" t="s">
         <v>57</v>
@@ -6349,7 +6358,7 @@
         <v>0032174C</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>57</v>
@@ -6384,7 +6393,7 @@
         <v>00321754</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C60" s="13" t="s">
         <v>58</v>
@@ -6395,7 +6404,7 @@
         <v>00321754</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>58</v>
